--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_39.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4027852.095306368</v>
+        <v>3987497.124861793</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6763872.953217702</v>
+        <v>6763872.953217701</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6763872.953217702</v>
+        <v>6763872.953217701</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3480075.510125574</v>
+        <v>3480075.510125575</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3480075.510125574</v>
+        <v>3480075.510125575</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50701653.64169682</v>
+        <v>50701653.64169681</v>
       </c>
     </row>
   </sheetData>
@@ -660,13 +660,13 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
         <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
-        <v>101.3800615824472</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G2" t="n">
         <v>403.7573722870162</v>
@@ -675,25 +675,25 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>97.45019138541491</v>
       </c>
       <c r="J2" t="n">
-        <v>798.7814999999999</v>
+        <v>419.7382696589336</v>
       </c>
       <c r="K2" t="n">
-        <v>767.4274152266737</v>
+        <v>783.0093003026869</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M2" t="n">
-        <v>298.9910820919849</v>
+        <v>610.7421986260833</v>
       </c>
       <c r="N2" t="n">
         <v>195.5855355810472</v>
       </c>
       <c r="O2" t="n">
-        <v>763.2897712690557</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>371.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.27058108003868</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -796,7 +796,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>32.37314290982852</v>
+        <v>288.415824755576</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -894,13 +894,13 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
-        <v>449.4745782429939</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
@@ -909,7 +909,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>355.3786904062574</v>
+        <v>104.5000915779626</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -918,19 +918,19 @@
         <v>419.7382696589336</v>
       </c>
       <c r="K5" t="n">
+        <v>66.13418277948216</v>
+      </c>
+      <c r="L5" t="n">
         <v>815</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>298.9910820919849</v>
       </c>
       <c r="N5" t="n">
-        <v>195.5855355810472</v>
+        <v>409.2117696382484</v>
       </c>
       <c r="O5" t="n">
-        <v>279.7604168367292</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>815</v>
@@ -939,13 +939,13 @@
         <v>371.9706110579117</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -957,10 +957,10 @@
         <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>192.3498461705184</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="7">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>449.4745782429939</v>
@@ -1137,7 +1137,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
@@ -1146,7 +1146,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>104.5000915779626</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -1155,16 +1155,16 @@
         <v>419.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>311.7511165340989</v>
+        <v>98.12488247690067</v>
       </c>
       <c r="L8" t="n">
-        <v>783.0093003026898</v>
+        <v>783.0093003026169</v>
       </c>
       <c r="M8" t="n">
         <v>298.9910820919849</v>
       </c>
       <c r="N8" t="n">
-        <v>195.5855355810472</v>
+        <v>409.2117696382464</v>
       </c>
       <c r="O8" t="n">
         <v>815</v>
@@ -1173,19 +1173,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>371.9706110579128</v>
+        <v>371.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>94.84816780232291</v>
+        <v>442.2171995050529</v>
       </c>
       <c r="T8" t="n">
         <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
-        <v>649.2212965486107</v>
+        <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1210,7 +1210,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>128.9988548477319</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
-        <v>419.8627394453875</v>
+        <v>77.58836382881024</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>61.69248475071642</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>185.3391557398498</v>
@@ -1377,13 +1377,13 @@
         <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1425,7 +1425,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>362.1583550136629</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>413.3734759809475</v>
@@ -1529,16 +1529,16 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
         <v>3.77112610161862</v>
@@ -1553,7 +1553,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>91.31217398560061</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>277.2560256873846</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>131.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>128.8134809922826</v>
+        <v>125.3632896068686</v>
       </c>
       <c r="F14" t="n">
         <v>125.8896287080119</v>
@@ -1620,7 +1620,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>129.0096587035274</v>
+        <v>132.4598500889414</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1769,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -1796,19 +1796,19 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>408.4478973282775</v>
+        <v>339.4016293563778</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>83.62701834505695</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>129.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.450191385413969</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.450191385414405</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>215.8481678023229</v>
@@ -2033,22 +2033,22 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>377.7929984536983</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>47.21655408469289</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H20" t="n">
-        <v>132.4598500889414</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.450191385414405</v>
       </c>
       <c r="S20" t="n">
         <v>215.8481678023229</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="P22" t="n">
-        <v>331.2878290192992</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>129.0096587035274</v>
+        <v>132.4598500889414</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>219.2983591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2507,19 +2507,19 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>47.21655408469291</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,19 +2550,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>155.7250107834309</v>
+        <v>74.91733470583537</v>
       </c>
       <c r="C26" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>178.7573722870162</v>
@@ -2604,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
         <v>424.2212965486107</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2753,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>345.9207354288559</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>340.7767994885276</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>115.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>120.0096587035274</v>
+        <v>109.7510500889419</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>47.83862152375353</v>
+        <v>47.83862152370034</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2841,7 +2841,7 @@
         <v>206.8481678023229</v>
       </c>
       <c r="T29" t="n">
-        <v>288.4169731139784</v>
+        <v>298.6755817285639</v>
       </c>
       <c r="U29" t="n">
         <v>361.2212965486107</v>
@@ -2984,19 +2984,19 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>352.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>102.9098435367298</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>380.9819279128893</v>
       </c>
       <c r="R31" t="n">
         <v>438.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>116.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>115.7573722870162</v>
+        <v>105.4987636724307</v>
       </c>
       <c r="H32" t="n">
         <v>120.0096587035274</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>47.83862152375353</v>
       </c>
       <c r="L32" t="n">
-        <v>47.83862152371154</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>196.5895591877376</v>
+        <v>206.8481678023229</v>
       </c>
       <c r="T32" t="n">
         <v>298.6755817285639</v>
@@ -3221,19 +3221,19 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>352.445564079015</v>
+        <v>55.90751028746737</v>
       </c>
       <c r="P34" t="n">
         <v>399.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>67.69059448674791</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>74.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
         <v>193.9993129555745</v>
       </c>
       <c r="C35" t="n">
-        <v>161.4745782429939</v>
+        <v>151.2159696284084</v>
       </c>
       <c r="D35" t="n">
         <v>122.3391557398498</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>47.83862152377593</v>
+        <v>47.83862152369522</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
         <v>341.8510241668239</v>
       </c>
       <c r="W35" t="n">
-        <v>340.1148673663618</v>
+        <v>350.3734759809475</v>
       </c>
       <c r="X35" t="n">
         <v>304.2818334606677</v>
@@ -3501,7 +3501,7 @@
         <v>193.9993129555745</v>
       </c>
       <c r="C38" t="n">
-        <v>161.4745782429939</v>
+        <v>151.2159696284084</v>
       </c>
       <c r="D38" t="n">
         <v>122.3391557398498</v>
@@ -3567,7 +3567,7 @@
         <v>304.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>213.0588240682208</v>
+        <v>223.3174326828064</v>
       </c>
     </row>
     <row r="39">
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>232.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -3698,16 +3698,16 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>223.4866577687479</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>437.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>438.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>17.51614119014671</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>291.9993129555745</v>
+        <v>153.1324597708169</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>259.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>220.3391557398498</v>
@@ -3747,13 +3747,13 @@
         <v>214.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>146.6418629353355</v>
+        <v>214.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>213.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>218.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>60.87859882829446</v>
       </c>
       <c r="S41" t="n">
         <v>304.8481678023229</v>
@@ -3792,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>459.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>439.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>448.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>402.2818334606677</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>194.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>171.0999124455193</v>
@@ -3826,13 +3826,13 @@
         <v>152.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>149.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>135.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>142.1680871864211</v>
+        <v>122.7436068698874</v>
       </c>
       <c r="I42" t="n">
         <v>27.12638589134853</v>
@@ -3862,22 +3862,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>219.286007140375</v>
+        <v>357.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>276.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>215.3577652175138</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>210.2103597601867</v>
       </c>
       <c r="V42" t="n">
         <v>224.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>242.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>229.8627394453875</v>
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>203.0171341045527</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3947,13 +3947,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>20.02456650625771</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>9.170310216216194</v>
       </c>
       <c r="W43" t="n">
         <v>0</v>
@@ -3975,10 +3975,10 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>376.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>337.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>331.3632896068686</v>
@@ -3987,13 +3987,13 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>330.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>335.0096587035274</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>4.291647590504849</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4023,16 +4023,16 @@
         <v>177.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>421.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>495.9203997134032</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>556.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>565.3734759809475</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>311.5565566463266</v>
+        <v>50.61172658197111</v>
       </c>
       <c r="C45" t="n">
-        <v>288.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4105,10 +4105,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>125.0283566956993</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>327.2103597601867</v>
       </c>
       <c r="V45" t="n">
         <v>341.5106671915202</v>
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>346.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>326.3913927661343</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>36.9802032459268</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4297,43 +4297,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1608.033611965038</v>
+        <v>1457.405934013821</v>
       </c>
       <c r="C2" t="n">
-        <v>1558.059290507469</v>
+        <v>1407.431612556251</v>
       </c>
       <c r="D2" t="n">
-        <v>1143.575294810651</v>
+        <v>1396.988020899837</v>
       </c>
       <c r="E2" t="n">
-        <v>735.1275275309853</v>
+        <v>988.5402536201722</v>
       </c>
       <c r="F2" t="n">
-        <v>632.7234249224528</v>
+        <v>579.5608306827864</v>
       </c>
       <c r="G2" t="n">
-        <v>224.8876953396081</v>
+        <v>171.7251010999418</v>
       </c>
       <c r="H2" t="n">
-        <v>216.7971309926107</v>
+        <v>163.6345367529444</v>
       </c>
       <c r="I2" t="n">
         <v>65.2</v>
       </c>
       <c r="J2" t="n">
-        <v>65.2</v>
+        <v>448.0719498394611</v>
       </c>
       <c r="K2" t="n">
-        <v>65.2</v>
+        <v>432.3326719848918</v>
       </c>
       <c r="L2" t="n">
-        <v>872.05</v>
+        <v>415.9503487525684</v>
       </c>
       <c r="M2" t="n">
-        <v>1376.888805967692</v>
+        <v>605.8890370090498</v>
       </c>
       <c r="N2" t="n">
-        <v>1986.177658916129</v>
+        <v>1215.177889957487</v>
       </c>
       <c r="O2" t="n">
         <v>2022.027889957487</v>
@@ -4345,28 +4345,28 @@
         <v>3260</v>
       </c>
       <c r="R2" t="n">
-        <v>3006.587273910814</v>
+        <v>3260</v>
       </c>
       <c r="S2" t="n">
-        <v>2910.781043807457</v>
+        <v>3164.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>2722.219850142241</v>
+        <v>2571.592172191024</v>
       </c>
       <c r="U2" t="n">
-        <v>2470.481166759806</v>
+        <v>2319.853488808589</v>
       </c>
       <c r="V2" t="n">
-        <v>2238.308415076146</v>
+        <v>2087.680737124928</v>
       </c>
       <c r="W2" t="n">
-        <v>1997.527126206502</v>
+        <v>1846.899448255284</v>
       </c>
       <c r="X2" t="n">
-        <v>1803.303052003807</v>
+        <v>1652.67537405259</v>
       </c>
       <c r="Y2" t="n">
-        <v>1690.861200809053</v>
+        <v>1540.233522857836</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>737.2967456696003</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="C3" t="n">
-        <v>737.2967456696003</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="D3" t="n">
-        <v>737.2967456696003</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="E3" t="n">
-        <v>737.2967456696003</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>394.2298342171994</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="H3" t="n">
-        <v>65.2</v>
+        <v>284.5195817084329</v>
       </c>
       <c r="I3" t="n">
         <v>65.2</v>
@@ -4421,31 +4421,31 @@
         <v>1220.632420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1045.804879873102</v>
+        <v>1220.632420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>897.0434684666577</v>
+        <v>1071.871008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>829.8071048660403</v>
+        <v>1004.634645361474</v>
       </c>
       <c r="T3" t="n">
-        <v>824.3952208079455</v>
+        <v>999.2227613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>824.1827362016962</v>
+        <v>999.0102766971303</v>
       </c>
       <c r="V3" t="n">
-        <v>809.5254966143021</v>
+        <v>984.3530371097362</v>
       </c>
       <c r="W3" t="n">
-        <v>776.82535226094</v>
+        <v>693.0239211950129</v>
       </c>
       <c r="X3" t="n">
-        <v>756.7619790837808</v>
+        <v>672.9605480178537</v>
       </c>
       <c r="Y3" t="n">
-        <v>756.7619790837808</v>
+        <v>672.9605480178537</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>942.8803972234075</v>
+        <v>301.271647980119</v>
       </c>
       <c r="C4" t="n">
-        <v>1068.882403041843</v>
+        <v>427.2736537985548</v>
       </c>
       <c r="D4" t="n">
-        <v>1068.882403041843</v>
+        <v>540.5927979235549</v>
       </c>
       <c r="E4" t="n">
-        <v>1068.882403041843</v>
+        <v>658.421702134968</v>
       </c>
       <c r="F4" t="n">
-        <v>1068.882403041843</v>
+        <v>782.7826747269035</v>
       </c>
       <c r="G4" t="n">
-        <v>1068.882403041843</v>
+        <v>782.7826747269035</v>
       </c>
       <c r="H4" t="n">
-        <v>1214.923502424373</v>
+        <v>952.299259886301</v>
       </c>
       <c r="I4" t="n">
-        <v>1214.923502424373</v>
+        <v>1173.432138822384</v>
       </c>
       <c r="J4" t="n">
-        <v>1576.007243076824</v>
+        <v>1534.515879474835</v>
       </c>
       <c r="K4" t="n">
         <v>1576.007243076824</v>
@@ -4512,19 +4512,19 @@
         <v>102.4502550941731</v>
       </c>
       <c r="U4" t="n">
-        <v>349.0014477324597</v>
+        <v>102.4502550941731</v>
       </c>
       <c r="V4" t="n">
-        <v>547.8228406184057</v>
+        <v>301.271647980119</v>
       </c>
       <c r="W4" t="n">
-        <v>719.7137588780831</v>
+        <v>301.271647980119</v>
       </c>
       <c r="X4" t="n">
-        <v>719.7137588780831</v>
+        <v>301.271647980119</v>
       </c>
       <c r="Y4" t="n">
-        <v>831.1230595571154</v>
+        <v>301.271647980119</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1053.365529973417</v>
+        <v>799.95280388423</v>
       </c>
       <c r="C5" t="n">
-        <v>599.3508044754429</v>
+        <v>749.9784824266603</v>
       </c>
       <c r="D5" t="n">
-        <v>588.907212819029</v>
+        <v>739.5348907702464</v>
       </c>
       <c r="E5" t="n">
-        <v>584.4998495797678</v>
+        <v>331.0871234905811</v>
       </c>
       <c r="F5" t="n">
-        <v>579.5608306827861</v>
+        <v>326.1481045935994</v>
       </c>
       <c r="G5" t="n">
-        <v>575.7655051403455</v>
+        <v>322.3527790511588</v>
       </c>
       <c r="H5" t="n">
         <v>216.7971309926107</v>
@@ -4561,19 +4561,19 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K5" t="n">
-        <v>431.6896266071377</v>
+        <v>1156.448952311257</v>
       </c>
       <c r="L5" t="n">
-        <v>1206.868833906741</v>
+        <v>1140.066629078934</v>
       </c>
       <c r="M5" t="n">
-        <v>1711.707639874433</v>
+        <v>1644.905435046626</v>
       </c>
       <c r="N5" t="n">
-        <v>2320.99649282287</v>
+        <v>2038.410213189809</v>
       </c>
       <c r="O5" t="n">
-        <v>2845.26021318981</v>
+        <v>2845.260213189809</v>
       </c>
       <c r="P5" t="n">
         <v>2828.877889957487</v>
@@ -4582,28 +4582,28 @@
         <v>3260</v>
       </c>
       <c r="R5" t="n">
-        <v>3260</v>
+        <v>3006.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>3164.193769896644</v>
+        <v>2506.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>2975.632576231427</v>
+        <v>1914.139042061433</v>
       </c>
       <c r="U5" t="n">
-        <v>2723.893892848992</v>
+        <v>1662.400358678998</v>
       </c>
       <c r="V5" t="n">
-        <v>2491.721141165332</v>
+        <v>1430.227606995337</v>
       </c>
       <c r="W5" t="n">
-        <v>2250.939852295688</v>
+        <v>1189.446318125693</v>
       </c>
       <c r="X5" t="n">
-        <v>1652.675374052589</v>
+        <v>995.2222439229986</v>
       </c>
       <c r="Y5" t="n">
-        <v>1136.193118817431</v>
+        <v>882.7803927282447</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>931.5895195792149</v>
+        <v>429.9473863086054</v>
       </c>
       <c r="C6" t="n">
-        <v>931.5895195792149</v>
+        <v>65.2</v>
       </c>
       <c r="D6" t="n">
-        <v>737.2967456696003</v>
+        <v>65.2</v>
       </c>
       <c r="E6" t="n">
-        <v>737.2967456696003</v>
+        <v>65.2</v>
       </c>
       <c r="F6" t="n">
-        <v>394.2298342171994</v>
+        <v>65.2</v>
       </c>
       <c r="G6" t="n">
         <v>65.2</v>
@@ -4682,7 +4682,7 @@
         <v>931.5895195792149</v>
       </c>
       <c r="Y6" t="n">
-        <v>931.5895195792149</v>
+        <v>818.3883526180261</v>
       </c>
     </row>
     <row r="7">
@@ -4692,25 +4692,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>955.0861890982213</v>
+        <v>808.2676350325895</v>
       </c>
       <c r="C7" t="n">
-        <v>1081.088194916657</v>
+        <v>808.2676350325895</v>
       </c>
       <c r="D7" t="n">
-        <v>1194.407339041657</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="E7" t="n">
-        <v>1312.23624325307</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="F7" t="n">
-        <v>1312.23624325307</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="G7" t="n">
-        <v>1465.642809139955</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="H7" t="n">
-        <v>1465.642809139955</v>
+        <v>1244.509930203872</v>
       </c>
       <c r="I7" t="n">
         <v>1465.642809139955</v>
@@ -4749,19 +4749,19 @@
         <v>290.525934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>382.0673668427575</v>
+        <v>290.525934252978</v>
       </c>
       <c r="V7" t="n">
-        <v>580.8887597287035</v>
+        <v>489.347327138924</v>
       </c>
       <c r="W7" t="n">
-        <v>580.8887597287035</v>
+        <v>489.347327138924</v>
       </c>
       <c r="X7" t="n">
-        <v>731.919550752897</v>
+        <v>585.1009966872651</v>
       </c>
       <c r="Y7" t="n">
-        <v>843.3288514319293</v>
+        <v>696.5102973662974</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>799.95280388423</v>
+        <v>1510.568528253487</v>
       </c>
       <c r="C8" t="n">
-        <v>345.9380783862563</v>
+        <v>1056.553802755514</v>
       </c>
       <c r="D8" t="n">
-        <v>335.4944867298424</v>
+        <v>1046.1102110991</v>
       </c>
       <c r="E8" t="n">
-        <v>331.0871234905811</v>
+        <v>637.6624438194344</v>
       </c>
       <c r="F8" t="n">
-        <v>326.1481045935994</v>
+        <v>632.7234249224528</v>
       </c>
       <c r="G8" t="n">
-        <v>322.3527790511588</v>
+        <v>628.9280993800121</v>
       </c>
       <c r="H8" t="n">
         <v>216.7971309926107</v>
@@ -4798,49 +4798,49 @@
         <v>448.0719498394611</v>
       </c>
       <c r="K8" t="n">
-        <v>940.02183212825</v>
+        <v>1155.805906933501</v>
       </c>
       <c r="L8" t="n">
-        <v>924.2825542736807</v>
+        <v>1140.066629078933</v>
       </c>
       <c r="M8" t="n">
-        <v>1429.121360241373</v>
+        <v>1644.905435046625</v>
       </c>
       <c r="N8" t="n">
         <v>2038.41021318981</v>
       </c>
       <c r="O8" t="n">
-        <v>2022.027889957486</v>
+        <v>2022.027889957487</v>
       </c>
       <c r="P8" t="n">
-        <v>2828.877889957486</v>
+        <v>2828.877889957487</v>
       </c>
       <c r="Q8" t="n">
         <v>3260</v>
       </c>
       <c r="R8" t="n">
-        <v>3006.587273910814</v>
+        <v>3260</v>
       </c>
       <c r="S8" t="n">
-        <v>2910.781043807457</v>
+        <v>2813.315960095906</v>
       </c>
       <c r="T8" t="n">
-        <v>2722.219850142241</v>
+        <v>2624.75476643069</v>
       </c>
       <c r="U8" t="n">
-        <v>2066.440762719402</v>
+        <v>2373.016083048255</v>
       </c>
       <c r="V8" t="n">
-        <v>1834.268011035741</v>
+        <v>2140.843331364595</v>
       </c>
       <c r="W8" t="n">
-        <v>1593.486722166097</v>
+        <v>1900.062042494951</v>
       </c>
       <c r="X8" t="n">
-        <v>1399.262647963403</v>
+        <v>1705.837968292256</v>
       </c>
       <c r="Y8" t="n">
-        <v>1286.820796768649</v>
+        <v>1593.396117097502</v>
       </c>
     </row>
     <row r="9">
@@ -4850,7 +4850,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>429.9473863086054</v>
+        <v>65.2</v>
       </c>
       <c r="C9" t="n">
         <v>65.2</v>
@@ -4907,19 +4907,19 @@
         <v>999.2227613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>999.0102766971303</v>
+        <v>594.9698726567262</v>
       </c>
       <c r="V9" t="n">
-        <v>984.3530371097362</v>
+        <v>580.3126330693322</v>
       </c>
       <c r="W9" t="n">
-        <v>854.0511635261686</v>
+        <v>143.5720846755659</v>
       </c>
       <c r="X9" t="n">
-        <v>429.9473863086054</v>
+        <v>65.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>429.9473863086054</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>971.0925923945239</v>
+        <v>440.0757524108052</v>
       </c>
       <c r="C10" t="n">
-        <v>1097.09459821296</v>
+        <v>566.077758229241</v>
       </c>
       <c r="D10" t="n">
-        <v>1097.09459821296</v>
+        <v>679.3969023542411</v>
       </c>
       <c r="E10" t="n">
-        <v>1214.923502424373</v>
+        <v>797.2258065656541</v>
       </c>
       <c r="F10" t="n">
-        <v>1214.923502424373</v>
+        <v>921.5867791575896</v>
       </c>
       <c r="G10" t="n">
-        <v>1214.923502424373</v>
+        <v>1074.993345044475</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.923502424373</v>
+        <v>1244.509930203872</v>
       </c>
       <c r="I10" t="n">
-        <v>1214.923502424373</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="J10" t="n">
-        <v>1576.007243076824</v>
+        <v>1465.642809139955</v>
       </c>
       <c r="K10" t="n">
         <v>1576.007243076824</v>
@@ -4986,19 +4986,19 @@
         <v>290.525934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>537.0771268912647</v>
+        <v>290.525934252978</v>
       </c>
       <c r="V10" t="n">
-        <v>708.6525006912981</v>
+        <v>328.3184147445131</v>
       </c>
       <c r="W10" t="n">
-        <v>708.6525006912981</v>
+        <v>328.3184147445131</v>
       </c>
       <c r="X10" t="n">
-        <v>859.6832917154916</v>
+        <v>328.3184147445131</v>
       </c>
       <c r="Y10" t="n">
-        <v>971.0925923945239</v>
+        <v>328.3184147445131</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1022.598004631051</v>
+        <v>618.4445495457029</v>
       </c>
       <c r="C11" t="n">
-        <v>795.8560064058046</v>
+        <v>618.4445495457029</v>
       </c>
       <c r="D11" t="n">
-        <v>608.6447379817139</v>
+        <v>431.2332811216122</v>
       </c>
       <c r="E11" t="n">
-        <v>427.4696979747758</v>
+        <v>250.0582411146742</v>
       </c>
       <c r="F11" t="n">
-        <v>245.7630023101174</v>
+        <v>250.0582411146742</v>
       </c>
       <c r="G11" t="n">
-        <v>65.2</v>
+        <v>250.0582411146742</v>
       </c>
       <c r="H11" t="n">
         <v>65.2</v>
@@ -5038,46 +5038,46 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1166.215479385524</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>1166.215479385524</v>
+        <v>1973.065479385524</v>
       </c>
       <c r="N11" t="n">
-        <v>1779.435799160287</v>
+        <v>2586.285799160287</v>
       </c>
       <c r="O11" t="n">
-        <v>2453.15</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P11" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3260</v>
       </c>
       <c r="R11" t="n">
-        <v>3260</v>
+        <v>3233.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3260</v>
+        <v>2961.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2894.671129567107</v>
+        <v>2595.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2466.164769416995</v>
+        <v>2167.450863729503</v>
       </c>
       <c r="V11" t="n">
-        <v>2100.348249201174</v>
+        <v>1758.510435278166</v>
       </c>
       <c r="W11" t="n">
-        <v>1682.799283563853</v>
+        <v>1340.961469640845</v>
       </c>
       <c r="X11" t="n">
-        <v>1311.807532593482</v>
+        <v>969.9697186704734</v>
       </c>
       <c r="Y11" t="n">
-        <v>1022.598004631051</v>
+        <v>680.7601907080427</v>
       </c>
     </row>
     <row r="12">
@@ -5114,22 +5114,22 @@
         <v>419.7013981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>831.6442142372473</v>
+        <v>627.8199167834982</v>
       </c>
       <c r="L12" t="n">
-        <v>1325.744675832447</v>
+        <v>1121.920378378698</v>
       </c>
       <c r="M12" t="n">
-        <v>1634.575217575307</v>
+        <v>1430.750920121558</v>
       </c>
       <c r="N12" t="n">
-        <v>1990.605502182875</v>
+        <v>1786.781204729126</v>
       </c>
       <c r="O12" t="n">
-        <v>2299.97518397327</v>
+        <v>2248.573656412845</v>
       </c>
       <c r="P12" t="n">
-        <v>2635.254528442777</v>
+        <v>2583.853000882351</v>
       </c>
       <c r="Q12" t="n">
         <v>2635.254528442777</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>177.5115880782802</v>
+        <v>256.8312907105077</v>
       </c>
       <c r="C13" t="n">
-        <v>177.5115880782802</v>
+        <v>256.8312907105077</v>
       </c>
       <c r="D13" t="n">
-        <v>177.5115880782802</v>
+        <v>195.6835957048961</v>
       </c>
       <c r="E13" t="n">
-        <v>177.5115880782802</v>
+        <v>139.1372271827178</v>
       </c>
       <c r="F13" t="n">
-        <v>177.5115880782802</v>
+        <v>89.25555448802895</v>
       </c>
       <c r="G13" t="n">
-        <v>177.5115880782802</v>
+        <v>69.00921828446326</v>
       </c>
       <c r="H13" t="n">
-        <v>173.7023697938169</v>
+        <v>65.2</v>
       </c>
       <c r="I13" t="n">
-        <v>221.5852487298998</v>
+        <v>113.0828789360829</v>
       </c>
       <c r="J13" t="n">
-        <v>409.4189893823511</v>
+        <v>300.9166195885342</v>
       </c>
       <c r="K13" t="n">
-        <v>345.2565916034188</v>
+        <v>236.7542218096019</v>
       </c>
       <c r="L13" t="n">
-        <v>345.2565916034188</v>
+        <v>144.5197026322275</v>
       </c>
       <c r="M13" t="n">
-        <v>345.2565916034188</v>
+        <v>144.5197026322275</v>
       </c>
       <c r="N13" t="n">
-        <v>345.2565916034188</v>
+        <v>144.5197026322275</v>
       </c>
       <c r="O13" t="n">
-        <v>65.2</v>
+        <v>144.5197026322275</v>
       </c>
       <c r="P13" t="n">
-        <v>65.2</v>
+        <v>144.5197026322275</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.2</v>
+        <v>144.5197026322275</v>
       </c>
       <c r="R13" t="n">
-        <v>65.2</v>
+        <v>144.5197026322275</v>
       </c>
       <c r="S13" t="n">
-        <v>65.2</v>
+        <v>144.5197026322275</v>
       </c>
       <c r="T13" t="n">
-        <v>80.02567915880486</v>
+        <v>159.3453817910324</v>
       </c>
       <c r="U13" t="n">
-        <v>153.3268717970915</v>
+        <v>232.646574429319</v>
       </c>
       <c r="V13" t="n">
-        <v>178.8982646830374</v>
+        <v>258.217967315265</v>
       </c>
       <c r="W13" t="n">
-        <v>177.5115880782802</v>
+        <v>256.8312907105077</v>
       </c>
       <c r="X13" t="n">
-        <v>177.5115880782802</v>
+        <v>256.8312907105077</v>
       </c>
       <c r="Y13" t="n">
-        <v>177.5115880782802</v>
+        <v>256.8312907105077</v>
       </c>
     </row>
     <row r="14">
@@ -5254,13 +5254,13 @@
         <v>578.8062027180183</v>
       </c>
       <c r="E14" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F14" t="n">
-        <v>321.5303343338825</v>
+        <v>325.0153761373309</v>
       </c>
       <c r="G14" t="n">
-        <v>195.5127865692196</v>
+        <v>198.9978283726681</v>
       </c>
       <c r="H14" t="n">
         <v>65.2</v>
@@ -5275,16 +5275,16 @@
         <v>1166.215479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1503.702076218397</v>
+        <v>1697.331756443634</v>
       </c>
       <c r="M14" t="n">
-        <v>2014.550904947333</v>
+        <v>2208.180585172569</v>
       </c>
       <c r="N14" t="n">
-        <v>2014.550904947333</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>2014.550904947333</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P14" t="n">
         <v>2821.400904947332</v>
@@ -5348,25 +5348,25 @@
         <v>65.2</v>
       </c>
       <c r="J15" t="n">
-        <v>189.156520175299</v>
+        <v>404.5252825072959</v>
       </c>
       <c r="K15" t="n">
-        <v>378.3493362696823</v>
+        <v>869.9280986016793</v>
       </c>
       <c r="L15" t="n">
-        <v>649.6997978648824</v>
+        <v>1141.278560196879</v>
       </c>
       <c r="M15" t="n">
-        <v>1011.990339607742</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N15" t="n">
-        <v>1145.27062421531</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O15" t="n">
-        <v>1660.523075899029</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P15" t="n">
-        <v>1773.052420368535</v>
+        <v>1712.211182700533</v>
       </c>
       <c r="Q15" t="n">
         <v>1817.072710260958</v>
@@ -5412,43 +5412,43 @@
         <v>428.8319797853442</v>
       </c>
       <c r="E16" t="n">
-        <v>426.8310658086205</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="F16" t="n">
-        <v>431.402038400556</v>
+        <v>433.4029523772797</v>
       </c>
       <c r="G16" t="n">
-        <v>465.0186042874412</v>
+        <v>467.019518264165</v>
       </c>
       <c r="H16" t="n">
-        <v>514.7451894468388</v>
+        <v>516.7461034235625</v>
       </c>
       <c r="I16" t="n">
-        <v>616.0880683829217</v>
+        <v>618.0889823596455</v>
       </c>
       <c r="J16" t="n">
-        <v>857.3818090353731</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="K16" t="n">
-        <v>857.3818090353731</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="L16" t="n">
-        <v>857.3818090353731</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="M16" t="n">
-        <v>857.3818090353731</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="N16" t="n">
-        <v>562.2453693670045</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O16" t="n">
-        <v>562.2453693670045</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P16" t="n">
-        <v>149.6717357020777</v>
+        <v>516.552794369291</v>
       </c>
       <c r="Q16" t="n">
-        <v>149.6717357020777</v>
+        <v>65.2</v>
       </c>
       <c r="R16" t="n">
         <v>65.2</v>
@@ -5482,25 +5482,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>880.1835184729979</v>
+        <v>883.6685602764463</v>
       </c>
       <c r="C17" t="n">
-        <v>707.9869747932061</v>
+        <v>711.4720165966545</v>
       </c>
       <c r="D17" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.5303343338825</v>
+        <v>325.0153761373309</v>
       </c>
       <c r="G17" t="n">
-        <v>195.5127865692196</v>
+        <v>198.9978283726681</v>
       </c>
       <c r="H17" t="n">
-        <v>65.2</v>
+        <v>68.68504180344846</v>
       </c>
       <c r="I17" t="n">
         <v>65.2</v>
@@ -5509,10 +5509,10 @@
         <v>456.5091130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>1166.215479385524</v>
+        <v>890.4817564436345</v>
       </c>
       <c r="L17" t="n">
-        <v>1401.330585172569</v>
+        <v>890.4817564436345</v>
       </c>
       <c r="M17" t="n">
         <v>1401.330585172569</v>
@@ -5530,28 +5530,28 @@
         <v>3260</v>
       </c>
       <c r="R17" t="n">
-        <v>3256.514958196551</v>
+        <v>3260</v>
       </c>
       <c r="S17" t="n">
-        <v>3038.486505870972</v>
+        <v>3041.971547674421</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.703089983534</v>
+        <v>2731.188131786983</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.742184378877</v>
+        <v>2357.227226182325</v>
       </c>
       <c r="V17" t="n">
-        <v>1999.347210472994</v>
+        <v>2002.832252276443</v>
       </c>
       <c r="W17" t="n">
-        <v>1636.343699381128</v>
+        <v>1639.828741184576</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.897402956211</v>
+        <v>1323.382444759659</v>
       </c>
       <c r="Y17" t="n">
-        <v>1085.233329539235</v>
+        <v>1088.718371342683</v>
       </c>
     </row>
     <row r="18">
@@ -5582,28 +5582,28 @@
         <v>65.2</v>
       </c>
       <c r="I18" t="n">
-        <v>126.454877967565</v>
+        <v>109.2202898924222</v>
       </c>
       <c r="J18" t="n">
-        <v>250.4113981428639</v>
+        <v>509.3868100677211</v>
       </c>
       <c r="K18" t="n">
-        <v>439.6042142372473</v>
+        <v>698.5796261621044</v>
       </c>
       <c r="L18" t="n">
-        <v>710.9546758324475</v>
+        <v>969.9300877573045</v>
       </c>
       <c r="M18" t="n">
-        <v>1073.245217575307</v>
+        <v>1056.010629500164</v>
       </c>
       <c r="N18" t="n">
-        <v>1360.639386547307</v>
+        <v>1189.290914107732</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.681838231026</v>
+        <v>1704.543365791451</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.211182700533</v>
+        <v>1817.072710260958</v>
       </c>
       <c r="Q18" t="n">
         <v>1817.072710260958</v>
@@ -5676,19 +5676,19 @@
         <v>859.3827230120968</v>
       </c>
       <c r="N19" t="n">
-        <v>564.2462833437282</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O19" t="n">
-        <v>564.2462833437282</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P19" t="n">
-        <v>564.2462833437282</v>
+        <v>446.80908934717</v>
       </c>
       <c r="Q19" t="n">
-        <v>112.8934889744373</v>
+        <v>65.2</v>
       </c>
       <c r="R19" t="n">
-        <v>112.8934889744373</v>
+        <v>65.2</v>
       </c>
       <c r="S19" t="n">
         <v>65.2</v>
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>883.6685602764463</v>
+        <v>880.1835184729979</v>
       </c>
       <c r="C20" t="n">
-        <v>711.4720165966545</v>
+        <v>707.9869747932061</v>
       </c>
       <c r="D20" t="n">
-        <v>578.8062027180183</v>
+        <v>575.3211609145699</v>
       </c>
       <c r="E20" t="n">
-        <v>452.1766172565348</v>
+        <v>448.6915754530864</v>
       </c>
       <c r="F20" t="n">
-        <v>325.0153761373309</v>
+        <v>321.5303343338825</v>
       </c>
       <c r="G20" t="n">
-        <v>198.9978283726681</v>
+        <v>195.5127865692196</v>
       </c>
       <c r="H20" t="n">
         <v>65.2</v>
@@ -5743,7 +5743,7 @@
         <v>65.2</v>
       </c>
       <c r="J20" t="n">
-        <v>456.5091130376557</v>
+        <v>180.775390095766</v>
       </c>
       <c r="K20" t="n">
         <v>890.4817564436344</v>
@@ -5767,28 +5767,28 @@
         <v>3260</v>
       </c>
       <c r="R20" t="n">
-        <v>3260</v>
+        <v>3256.514958196551</v>
       </c>
       <c r="S20" t="n">
-        <v>3041.971547674421</v>
+        <v>3038.486505870972</v>
       </c>
       <c r="T20" t="n">
-        <v>2731.188131786983</v>
+        <v>2727.703089983534</v>
       </c>
       <c r="U20" t="n">
-        <v>2357.227226182325</v>
+        <v>2353.742184378877</v>
       </c>
       <c r="V20" t="n">
-        <v>2002.832252276443</v>
+        <v>1999.347210472994</v>
       </c>
       <c r="W20" t="n">
-        <v>1639.828741184576</v>
+        <v>1636.343699381128</v>
       </c>
       <c r="X20" t="n">
-        <v>1323.382444759659</v>
+        <v>1319.897402956211</v>
       </c>
       <c r="Y20" t="n">
-        <v>1088.718371342683</v>
+        <v>1085.233329539235</v>
       </c>
     </row>
     <row r="21">
@@ -5819,25 +5819,25 @@
         <v>65.2</v>
       </c>
       <c r="I21" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>189.156520175299</v>
+        <v>250.4113981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>378.3493362696823</v>
+        <v>439.6042142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>649.6997978648824</v>
+        <v>987.1646758324475</v>
       </c>
       <c r="M21" t="n">
-        <v>735.7803396077417</v>
+        <v>1227.359101939739</v>
       </c>
       <c r="N21" t="n">
-        <v>1084.429386547307</v>
+        <v>1360.639386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1323.471838231026</v>
+        <v>1599.681838231026</v>
       </c>
       <c r="P21" t="n">
         <v>1712.211182700533</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>414.4242160506674</v>
+        <v>422.6199739669084</v>
       </c>
       <c r="C22" t="n">
-        <v>420.6362218691032</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="D22" t="n">
-        <v>420.6362218691032</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="E22" t="n">
-        <v>420.6362218691032</v>
+        <v>428.8319797853442</v>
       </c>
       <c r="F22" t="n">
-        <v>425.2071944610387</v>
+        <v>433.4029523772797</v>
       </c>
       <c r="G22" t="n">
-        <v>458.823760347924</v>
+        <v>467.019518264165</v>
       </c>
       <c r="H22" t="n">
-        <v>508.5503455073215</v>
+        <v>516.7461034235625</v>
       </c>
       <c r="I22" t="n">
-        <v>609.8932244434045</v>
+        <v>618.0889823596455</v>
       </c>
       <c r="J22" t="n">
-        <v>851.1869650958558</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="K22" t="n">
-        <v>851.1869650958558</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="L22" t="n">
-        <v>851.1869650958558</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="M22" t="n">
-        <v>851.1869650958558</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="N22" t="n">
-        <v>851.1869650958558</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O22" t="n">
-        <v>851.1869650958558</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="P22" t="n">
-        <v>516.552794369291</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="Q22" t="n">
-        <v>65.2</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="R22" t="n">
         <v>65.2</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>880.1835184729979</v>
+        <v>883.6685602764463</v>
       </c>
       <c r="C23" t="n">
-        <v>707.9869747932061</v>
+        <v>711.4720165966545</v>
       </c>
       <c r="D23" t="n">
-        <v>575.3211609145699</v>
+        <v>578.8062027180183</v>
       </c>
       <c r="E23" t="n">
-        <v>448.6915754530864</v>
+        <v>452.1766172565348</v>
       </c>
       <c r="F23" t="n">
-        <v>321.5303343338825</v>
+        <v>325.0153761373309</v>
       </c>
       <c r="G23" t="n">
-        <v>195.5127865692196</v>
+        <v>198.9978283726681</v>
       </c>
       <c r="H23" t="n">
         <v>65.2</v>
@@ -5983,22 +5983,22 @@
         <v>456.5091130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>522.230851496302</v>
+        <v>456.5091130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1329.080851496302</v>
+        <v>890.4817564436345</v>
       </c>
       <c r="M23" t="n">
-        <v>1839.929680225237</v>
+        <v>1401.330585172569</v>
       </c>
       <c r="N23" t="n">
-        <v>2453.15</v>
+        <v>2014.550904947333</v>
       </c>
       <c r="O23" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="P23" t="n">
-        <v>3260</v>
+        <v>2821.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>3260</v>
@@ -6007,25 +6007,25 @@
         <v>3260</v>
       </c>
       <c r="S23" t="n">
-        <v>3038.486505870972</v>
+        <v>3041.971547674421</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.703089983534</v>
+        <v>2731.188131786983</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.742184378877</v>
+        <v>2357.227226182325</v>
       </c>
       <c r="V23" t="n">
-        <v>1999.347210472994</v>
+        <v>2002.832252276443</v>
       </c>
       <c r="W23" t="n">
-        <v>1636.343699381128</v>
+        <v>1639.828741184576</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.897402956211</v>
+        <v>1323.382444759659</v>
       </c>
       <c r="Y23" t="n">
-        <v>1085.233329539235</v>
+        <v>1088.718371342683</v>
       </c>
     </row>
     <row r="24">
@@ -6056,19 +6056,19 @@
         <v>65.2</v>
       </c>
       <c r="I24" t="n">
-        <v>65.2</v>
+        <v>126.454877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>465.3665201752989</v>
+        <v>526.6213981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>869.9280986016793</v>
+        <v>715.8142142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>1141.278560196879</v>
+        <v>987.1646758324473</v>
       </c>
       <c r="M24" t="n">
-        <v>1227.359101939739</v>
+        <v>1073.245217575306</v>
       </c>
       <c r="N24" t="n">
         <v>1360.639386547307</v>
@@ -6150,16 +6150,16 @@
         <v>859.3827230120968</v>
       </c>
       <c r="N25" t="n">
-        <v>564.2462833437282</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="O25" t="n">
-        <v>564.2462833437282</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="P25" t="n">
-        <v>516.552794369291</v>
+        <v>859.3827230120968</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.2</v>
+        <v>517.3233615971224</v>
       </c>
       <c r="R25" t="n">
         <v>65.2</v>
@@ -6193,16 +6193,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1017.364977321634</v>
+        <v>1022.869550081067</v>
       </c>
       <c r="C26" t="n">
-        <v>790.622979096388</v>
+        <v>796.1275518558203</v>
       </c>
       <c r="D26" t="n">
-        <v>790.622979096388</v>
+        <v>608.9162834317297</v>
       </c>
       <c r="E26" t="n">
-        <v>609.44793908945</v>
+        <v>427.7412434247915</v>
       </c>
       <c r="F26" t="n">
         <v>427.7412434247915</v>
@@ -6223,19 +6223,19 @@
         <v>772.0263663478684</v>
       </c>
       <c r="L26" t="n">
-        <v>1220.720851496278</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="M26" t="n">
-        <v>1731.569680225213</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="N26" t="n">
-        <v>2344.789999999976</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="O26" t="n">
-        <v>3116</v>
+        <v>1906.190904947308</v>
       </c>
       <c r="P26" t="n">
-        <v>3116</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="Q26" t="n">
         <v>3116</v>
@@ -6247,22 +6247,22 @@
         <v>3089.860001183541</v>
       </c>
       <c r="T26" t="n">
-        <v>3089.860001183541</v>
+        <v>2724.531130750648</v>
       </c>
       <c r="U26" t="n">
-        <v>2661.353641033429</v>
+        <v>2296.024770600536</v>
       </c>
       <c r="V26" t="n">
-        <v>2252.413212582092</v>
+        <v>1887.084342149199</v>
       </c>
       <c r="W26" t="n">
-        <v>1834.864246944771</v>
+        <v>1469.535376511878</v>
       </c>
       <c r="X26" t="n">
-        <v>1463.872495974399</v>
+        <v>1098.543625541507</v>
       </c>
       <c r="Y26" t="n">
-        <v>1174.662968011969</v>
+        <v>1098.543625541507</v>
       </c>
     </row>
     <row r="27">
@@ -6299,7 +6299,7 @@
         <v>416.8213981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>624.9399167834981</v>
+        <v>828.7642142372474</v>
       </c>
       <c r="L27" t="n">
         <v>1119.040378378698</v>
@@ -6351,52 +6351,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="G28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="H28" t="n">
-        <v>176.0182646830374</v>
+        <v>170.8223697938169</v>
       </c>
       <c r="I28" t="n">
-        <v>223.9011436191203</v>
+        <v>218.7052487298998</v>
       </c>
       <c r="J28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="K28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="L28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="M28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="N28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="O28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="P28" t="n">
-        <v>411.7348842715717</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="Q28" t="n">
-        <v>62.32</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="R28" t="n">
         <v>62.32</v>
@@ -6414,13 +6414,13 @@
         <v>176.0182646830374</v>
       </c>
       <c r="W28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>176.0182646830374</v>
+        <v>174.6315880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>822.7580639275434</v>
+        <v>812.3958330037195</v>
       </c>
       <c r="C29" t="n">
-        <v>659.6524293386606</v>
+        <v>649.2901984148368</v>
       </c>
       <c r="D29" t="n">
-        <v>536.0775245509335</v>
+        <v>525.7152936271098</v>
       </c>
       <c r="E29" t="n">
-        <v>418.5388481803591</v>
+        <v>408.1766172565353</v>
       </c>
       <c r="F29" t="n">
-        <v>300.4685161520642</v>
+        <v>290.1062852282405</v>
       </c>
       <c r="G29" t="n">
-        <v>183.5418774783105</v>
+        <v>173.1796465544867</v>
       </c>
       <c r="H29" t="n">
         <v>62.32</v>
@@ -6457,22 +6457,22 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>452.6675084231883</v>
+        <v>1162.373874771058</v>
       </c>
       <c r="L29" t="n">
-        <v>452.6675084231883</v>
+        <v>1933.583874771058</v>
       </c>
       <c r="M29" t="n">
-        <v>963.5163371521234</v>
+        <v>2444.432703499993</v>
       </c>
       <c r="N29" t="n">
-        <v>1576.736656926887</v>
+        <v>3057.653023274756</v>
       </c>
       <c r="O29" t="n">
-        <v>1906.190904947302</v>
+        <v>3116</v>
       </c>
       <c r="P29" t="n">
-        <v>2677.400904947332</v>
+        <v>3116</v>
       </c>
       <c r="Q29" t="n">
         <v>3116</v>
@@ -6484,22 +6484,22 @@
         <v>2907.06245676533</v>
       </c>
       <c r="T29" t="n">
-        <v>2615.732180892625</v>
+        <v>2605.369949968801</v>
       </c>
       <c r="U29" t="n">
-        <v>2250.862184378877</v>
+        <v>2240.499953455053</v>
       </c>
       <c r="V29" t="n">
-        <v>1905.558119563903</v>
+        <v>1895.195888640079</v>
       </c>
       <c r="W29" t="n">
-        <v>1551.645517562946</v>
+        <v>1541.283286639122</v>
       </c>
       <c r="X29" t="n">
-        <v>1244.290130228938</v>
+        <v>1233.927899305114</v>
       </c>
       <c r="Y29" t="n">
-        <v>1018.716965902871</v>
+        <v>1008.354734979047</v>
       </c>
     </row>
     <row r="30">
@@ -6539,13 +6539,13 @@
         <v>375.4693362696823</v>
       </c>
       <c r="L30" t="n">
-        <v>821.7764513936685</v>
+        <v>646.8197978648825</v>
       </c>
       <c r="M30" t="n">
-        <v>907.8569931365278</v>
+        <v>732.9003396077418</v>
       </c>
       <c r="N30" t="n">
-        <v>1041.137277744096</v>
+        <v>866.1806242153101</v>
       </c>
       <c r="O30" t="n">
         <v>1280.179729427815</v>
@@ -6627,16 +6627,16 @@
         <v>965.3074096938342</v>
       </c>
       <c r="O31" t="n">
-        <v>609.3017894120009</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="P31" t="n">
-        <v>505.3524525062132</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="Q31" t="n">
-        <v>505.3524525062132</v>
+        <v>580.4771794787945</v>
       </c>
       <c r="R31" t="n">
-        <v>62.32</v>
+        <v>137.4447269725813</v>
       </c>
       <c r="S31" t="n">
         <v>62.32</v>
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>822.7580639275434</v>
+        <v>812.3958330037195</v>
       </c>
       <c r="C32" t="n">
-        <v>659.6524293386606</v>
+        <v>649.2901984148368</v>
       </c>
       <c r="D32" t="n">
-        <v>536.0775245509335</v>
+        <v>525.7152936271098</v>
       </c>
       <c r="E32" t="n">
-        <v>418.5388481803591</v>
+        <v>408.1766172565353</v>
       </c>
       <c r="F32" t="n">
-        <v>300.4685161520642</v>
+        <v>290.1062852282405</v>
       </c>
       <c r="G32" t="n">
         <v>183.5418774783105</v>
@@ -6694,19 +6694,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>1135.942509561717</v>
+        <v>452.6675084231883</v>
       </c>
       <c r="L32" t="n">
-        <v>1134.98090494725</v>
+        <v>452.6675084231883</v>
       </c>
       <c r="M32" t="n">
-        <v>1134.98090494725</v>
+        <v>963.5163371521234</v>
       </c>
       <c r="N32" t="n">
-        <v>1134.98090494725</v>
+        <v>1576.736656926887</v>
       </c>
       <c r="O32" t="n">
-        <v>1906.190904947291</v>
+        <v>1906.190904947292</v>
       </c>
       <c r="P32" t="n">
         <v>2677.400904947332</v>
@@ -6718,25 +6718,25 @@
         <v>3116</v>
       </c>
       <c r="S32" t="n">
-        <v>2917.424687689154</v>
+        <v>2907.06245676533</v>
       </c>
       <c r="T32" t="n">
-        <v>2615.732180892625</v>
+        <v>2605.369949968801</v>
       </c>
       <c r="U32" t="n">
-        <v>2250.862184378877</v>
+        <v>2240.499953455053</v>
       </c>
       <c r="V32" t="n">
-        <v>1905.558119563903</v>
+        <v>1895.195888640079</v>
       </c>
       <c r="W32" t="n">
-        <v>1551.645517562946</v>
+        <v>1541.283286639122</v>
       </c>
       <c r="X32" t="n">
-        <v>1244.290130228938</v>
+        <v>1233.927899305114</v>
       </c>
       <c r="Y32" t="n">
-        <v>1018.716965902871</v>
+        <v>1008.354734979047</v>
       </c>
     </row>
     <row r="33">
@@ -6770,16 +6770,16 @@
         <v>132.484877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>361.2331737040851</v>
+        <v>256.4413981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>550.4259897984684</v>
+        <v>730.7542142372474</v>
       </c>
       <c r="L33" t="n">
-        <v>821.7764513936685</v>
+        <v>1002.104675832448</v>
       </c>
       <c r="M33" t="n">
-        <v>907.8569931365278</v>
+        <v>1192.976993136528</v>
       </c>
       <c r="N33" t="n">
         <v>1326.257277744096</v>
@@ -6864,16 +6864,16 @@
         <v>965.3074096938342</v>
       </c>
       <c r="O34" t="n">
-        <v>609.3017894120009</v>
+        <v>908.8351770802308</v>
       </c>
       <c r="P34" t="n">
-        <v>205.8190648379832</v>
+        <v>505.3524525062132</v>
       </c>
       <c r="Q34" t="n">
-        <v>137.4447269725813</v>
+        <v>505.3524525062132</v>
       </c>
       <c r="R34" t="n">
-        <v>137.4447269725813</v>
+        <v>62.32</v>
       </c>
       <c r="S34" t="n">
         <v>62.32</v>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>822.7580639275434</v>
+        <v>812.3958330037195</v>
       </c>
       <c r="C35" t="n">
         <v>659.6524293386606</v>
@@ -6928,22 +6928,22 @@
         <v>62.32</v>
       </c>
       <c r="J35" t="n">
-        <v>453.6291130376557</v>
+        <v>120.7372300186904</v>
       </c>
       <c r="K35" t="n">
-        <v>453.6291130376557</v>
+        <v>830.4435963665588</v>
       </c>
       <c r="L35" t="n">
-        <v>452.6675084231879</v>
+        <v>1553.331756443634</v>
       </c>
       <c r="M35" t="n">
-        <v>963.5163371521229</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N35" t="n">
-        <v>1576.736656926886</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>2347.946656926947</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P35" t="n">
         <v>2677.400904947332</v>
@@ -6967,13 +6967,13 @@
         <v>1895.195888640079</v>
       </c>
       <c r="W35" t="n">
-        <v>1551.645517562946</v>
+        <v>1541.283286639122</v>
       </c>
       <c r="X35" t="n">
-        <v>1244.290130228938</v>
+        <v>1233.927899305114</v>
       </c>
       <c r="Y35" t="n">
-        <v>1018.716965902871</v>
+        <v>1008.354734979047</v>
       </c>
     </row>
     <row r="36">
@@ -7004,28 +7004,28 @@
         <v>62.32</v>
       </c>
       <c r="I36" t="n">
-        <v>62.32</v>
+        <v>123.5051259683604</v>
       </c>
       <c r="J36" t="n">
-        <v>186.2765201752989</v>
+        <v>247.4616461436594</v>
       </c>
       <c r="K36" t="n">
-        <v>375.4693362696823</v>
+        <v>436.6544622380428</v>
       </c>
       <c r="L36" t="n">
-        <v>931.9397978648825</v>
+        <v>708.0049238332429</v>
       </c>
       <c r="M36" t="n">
-        <v>1018.020339607742</v>
+        <v>794.0854655761021</v>
       </c>
       <c r="N36" t="n">
-        <v>1151.30062421531</v>
+        <v>927.3657501836705</v>
       </c>
       <c r="O36" t="n">
-        <v>1390.343075899029</v>
+        <v>1166.408201867389</v>
       </c>
       <c r="P36" t="n">
-        <v>1677.829073897321</v>
+        <v>1564.057546336896</v>
       </c>
       <c r="Q36" t="n">
         <v>1677.829073897321</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>822.7580639275434</v>
+        <v>812.3958330037195</v>
       </c>
       <c r="C38" t="n">
         <v>659.6524293386606</v>
@@ -7171,13 +7171,13 @@
         <v>1163.335479385524</v>
       </c>
       <c r="L38" t="n">
-        <v>1395.342076218323</v>
+        <v>1553.331756443634</v>
       </c>
       <c r="M38" t="n">
-        <v>1906.190904947258</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N38" t="n">
-        <v>1906.190904947258</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O38" t="n">
         <v>2677.400904947332</v>
@@ -7210,7 +7210,7 @@
         <v>1233.927899305114</v>
       </c>
       <c r="Y38" t="n">
-        <v>1018.716965902871</v>
+        <v>1008.354734979047</v>
       </c>
     </row>
     <row r="39">
@@ -7241,28 +7241,28 @@
         <v>62.32</v>
       </c>
       <c r="I39" t="n">
-        <v>62.32</v>
+        <v>132.484877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>186.2765201752989</v>
+        <v>256.4413981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>550.4259897984682</v>
+        <v>730.7542142372474</v>
       </c>
       <c r="L39" t="n">
-        <v>821.7764513936683</v>
+        <v>1002.104675832448</v>
       </c>
       <c r="M39" t="n">
-        <v>907.8569931365275</v>
+        <v>1088.185217575307</v>
       </c>
       <c r="N39" t="n">
-        <v>1041.137277744096</v>
+        <v>1221.465502182875</v>
       </c>
       <c r="O39" t="n">
-        <v>1565.299729427815</v>
+        <v>1460.507953866594</v>
       </c>
       <c r="P39" t="n">
-        <v>1677.829073897321</v>
+        <v>1573.037298336101</v>
       </c>
       <c r="Q39" t="n">
         <v>1677.829073897321</v>
@@ -7332,22 +7332,22 @@
         <v>965.3074096938342</v>
       </c>
       <c r="M40" t="n">
-        <v>730.3259840346929</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="N40" t="n">
-        <v>730.3259840346929</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="O40" t="n">
-        <v>730.3259840346929</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="P40" t="n">
-        <v>504.5818852783818</v>
+        <v>965.3074096938342</v>
       </c>
       <c r="Q40" t="n">
-        <v>62.32</v>
+        <v>523.0455244154523</v>
       </c>
       <c r="R40" t="n">
-        <v>62.32</v>
+        <v>80.0130719092391</v>
       </c>
       <c r="S40" t="n">
         <v>62.32</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>865.4530106758284</v>
+        <v>1416.697457866937</v>
       </c>
       <c r="C41" t="n">
-        <v>865.4530106758284</v>
+        <v>1154.601924288155</v>
       </c>
       <c r="D41" t="n">
-        <v>642.8882068982024</v>
+        <v>932.0371205105295</v>
       </c>
       <c r="E41" t="n">
-        <v>426.359631537729</v>
+        <v>715.5085451500561</v>
       </c>
       <c r="F41" t="n">
-        <v>278.2365376636528</v>
+        <v>498.4483141318623</v>
       </c>
       <c r="G41" t="n">
-        <v>62.32</v>
+        <v>282.5317764682095</v>
       </c>
       <c r="H41" t="n">
         <v>62.32</v>
@@ -7402,52 +7402,52 @@
         <v>62.32</v>
       </c>
       <c r="J41" t="n">
-        <v>62.32</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>772.0263663478684</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L41" t="n">
-        <v>772.0263663478684</v>
+        <v>1906.190904947223</v>
       </c>
       <c r="M41" t="n">
-        <v>772.0263663478684</v>
+        <v>1906.190904947223</v>
       </c>
       <c r="N41" t="n">
-        <v>1385.246686122632</v>
+        <v>1906.190904947223</v>
       </c>
       <c r="O41" t="n">
-        <v>2156.456686122742</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P41" t="n">
-        <v>2927.666686122852</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>3116</v>
       </c>
       <c r="R41" t="n">
-        <v>3116</v>
+        <v>3054.506465830006</v>
       </c>
       <c r="S41" t="n">
-        <v>2808.072557775432</v>
+        <v>2746.579023605437</v>
       </c>
       <c r="T41" t="n">
-        <v>2808.072557775432</v>
+        <v>2746.579023605437</v>
       </c>
       <c r="U41" t="n">
-        <v>2344.212662271784</v>
+        <v>2746.579023605437</v>
       </c>
       <c r="V41" t="n">
-        <v>2344.212662271784</v>
+        <v>2302.285059800564</v>
       </c>
       <c r="W41" t="n">
-        <v>1891.310161280928</v>
+        <v>2302.285059800564</v>
       </c>
       <c r="X41" t="n">
-        <v>1484.964874957021</v>
+        <v>1895.939773476658</v>
       </c>
       <c r="Y41" t="n">
-        <v>1160.401811641055</v>
+        <v>1571.376710160692</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1008.158331167483</v>
+        <v>700.2792821478489</v>
       </c>
       <c r="C42" t="n">
-        <v>835.3301367780698</v>
+        <v>527.4510877584355</v>
       </c>
       <c r="D42" t="n">
-        <v>675.7971197096833</v>
+        <v>367.918070690049</v>
       </c>
       <c r="E42" t="n">
-        <v>521.5828800915898</v>
+        <v>213.7038310719555</v>
       </c>
       <c r="F42" t="n">
-        <v>370.4351605583809</v>
+        <v>213.7038310719555</v>
       </c>
       <c r="G42" t="n">
-        <v>233.3245182603734</v>
+        <v>213.7038310719555</v>
       </c>
       <c r="H42" t="n">
         <v>89.72038978924094</v>
@@ -7481,52 +7481,52 @@
         <v>62.32</v>
       </c>
       <c r="J42" t="n">
-        <v>374.3765201752989</v>
+        <v>264.0283408969486</v>
       </c>
       <c r="K42" t="n">
-        <v>563.5693362696824</v>
+        <v>641.3211569913319</v>
       </c>
       <c r="L42" t="n">
-        <v>1023.019797864883</v>
+        <v>1100.771618586532</v>
       </c>
       <c r="M42" t="n">
-        <v>1297.200339607742</v>
+        <v>1374.952160329391</v>
       </c>
       <c r="N42" t="n">
-        <v>1618.58062421531</v>
+        <v>1696.33244493696</v>
       </c>
       <c r="O42" t="n">
-        <v>2040.842629222797</v>
+        <v>2123.474896620678</v>
       </c>
       <c r="P42" t="n">
-        <v>2341.471973692303</v>
+        <v>2424.104241090185</v>
       </c>
       <c r="Q42" t="n">
-        <v>2341.471973692303</v>
+        <v>2440.85576865061</v>
       </c>
       <c r="R42" t="n">
-        <v>2119.970956378793</v>
+        <v>2079.973145122954</v>
       </c>
       <c r="S42" t="n">
-        <v>2119.970956378793</v>
+        <v>1800.615569401125</v>
       </c>
       <c r="T42" t="n">
-        <v>2119.970956378793</v>
+        <v>1583.082473221818</v>
       </c>
       <c r="U42" t="n">
-        <v>2119.970956378793</v>
+        <v>1370.748776494356</v>
       </c>
       <c r="V42" t="n">
-        <v>1893.192504670187</v>
+        <v>1143.97032478575</v>
       </c>
       <c r="W42" t="n">
-        <v>1648.371148195613</v>
+        <v>1143.97032478575</v>
       </c>
       <c r="X42" t="n">
-        <v>1416.186562897242</v>
+        <v>911.7857394873786</v>
       </c>
       <c r="Y42" t="n">
-        <v>1204.680105557712</v>
+        <v>700.2792821478489</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>100.9711926382866</v>
+        <v>62.32</v>
       </c>
       <c r="C43" t="n">
-        <v>100.9711926382866</v>
+        <v>62.32</v>
       </c>
       <c r="D43" t="n">
-        <v>100.9711926382866</v>
+        <v>62.32</v>
       </c>
       <c r="E43" t="n">
-        <v>100.9711926382866</v>
+        <v>62.32</v>
       </c>
       <c r="F43" t="n">
-        <v>100.9711926382866</v>
+        <v>62.32</v>
       </c>
       <c r="G43" t="n">
-        <v>100.9711926382866</v>
+        <v>62.32</v>
       </c>
       <c r="H43" t="n">
-        <v>100.9711926382866</v>
+        <v>62.32</v>
       </c>
       <c r="I43" t="n">
-        <v>114.2040715743696</v>
+        <v>62.32</v>
       </c>
       <c r="J43" t="n">
-        <v>267.3878122268209</v>
+        <v>91.80977446714536</v>
       </c>
       <c r="K43" t="n">
-        <v>267.3878122268209</v>
+        <v>91.80977446714536</v>
       </c>
       <c r="L43" t="n">
-        <v>267.3878122268209</v>
+        <v>91.80977446714536</v>
       </c>
       <c r="M43" t="n">
-        <v>267.3878122268209</v>
+        <v>91.80977446714536</v>
       </c>
       <c r="N43" t="n">
-        <v>267.3878122268209</v>
+        <v>91.80977446714536</v>
       </c>
       <c r="O43" t="n">
-        <v>267.3878122268209</v>
+        <v>91.80977446714536</v>
       </c>
       <c r="P43" t="n">
-        <v>267.3878122268209</v>
+        <v>91.80977446714536</v>
       </c>
       <c r="Q43" t="n">
+        <v>91.80977446714536</v>
+      </c>
+      <c r="R43" t="n">
+        <v>91.80977446714536</v>
+      </c>
+      <c r="S43" t="n">
+        <v>91.80977446714536</v>
+      </c>
+      <c r="T43" t="n">
+        <v>71.58293961233959</v>
+      </c>
+      <c r="U43" t="n">
+        <v>71.58293961233959</v>
+      </c>
+      <c r="V43" t="n">
         <v>62.32</v>
       </c>
-      <c r="R43" t="n">
+      <c r="W43" t="n">
         <v>62.32</v>
       </c>
-      <c r="S43" t="n">
+      <c r="X43" t="n">
         <v>62.32</v>
       </c>
-      <c r="T43" t="n">
+      <c r="Y43" t="n">
         <v>62.32</v>
-      </c>
-      <c r="U43" t="n">
-        <v>100.9711926382866</v>
-      </c>
-      <c r="V43" t="n">
-        <v>100.9711926382866</v>
-      </c>
-      <c r="W43" t="n">
-        <v>100.9711926382866</v>
-      </c>
-      <c r="X43" t="n">
-        <v>100.9711926382866</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>100.9711926382866</v>
       </c>
     </row>
     <row r="44">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>777.3077453028915</v>
+        <v>1414.603963563401</v>
       </c>
       <c r="C44" t="n">
-        <v>397.0303935422916</v>
+        <v>1414.603963563401</v>
       </c>
       <c r="D44" t="n">
-        <v>397.0303935422916</v>
+        <v>1073.857341603957</v>
       </c>
       <c r="E44" t="n">
-        <v>62.32</v>
+        <v>739.1469480616652</v>
       </c>
       <c r="F44" t="n">
-        <v>62.32</v>
+        <v>739.1469480616652</v>
       </c>
       <c r="G44" t="n">
-        <v>62.32</v>
+        <v>405.0485922161942</v>
       </c>
       <c r="H44" t="n">
-        <v>62.32</v>
+        <v>66.65499756616651</v>
       </c>
       <c r="I44" t="n">
         <v>62.32</v>
@@ -7642,19 +7642,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>453.6291130376557</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L44" t="n">
-        <v>1134.98090494702</v>
+        <v>1934.545479385524</v>
       </c>
       <c r="M44" t="n">
-        <v>1134.98090494702</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N44" t="n">
-        <v>1134.98090494702</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>1906.190904947176</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P44" t="n">
         <v>2677.400904947332</v>
@@ -7666,25 +7666,25 @@
         <v>2936.324647648187</v>
       </c>
       <c r="S44" t="n">
-        <v>2936.324647648187</v>
+        <v>2510.2153872418</v>
       </c>
       <c r="T44" t="n">
-        <v>2435.394950967982</v>
+        <v>2510.2153872418</v>
       </c>
       <c r="U44" t="n">
-        <v>2435.394950967982</v>
+        <v>2510.2153872418</v>
       </c>
       <c r="V44" t="n">
-        <v>1872.919168981291</v>
+        <v>2510.2153872418</v>
       </c>
       <c r="W44" t="n">
-        <v>1301.834849808617</v>
+        <v>1939.131068069126</v>
       </c>
       <c r="X44" t="n">
-        <v>777.3077453028915</v>
+        <v>1414.603963563401</v>
       </c>
       <c r="Y44" t="n">
-        <v>777.3077453028915</v>
+        <v>1414.603963563401</v>
       </c>
     </row>
     <row r="45">
@@ -7694,7 +7694,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>498.9122205422908</v>
+        <v>207.9022079710591</v>
       </c>
       <c r="C45" t="n">
         <v>207.9022079710591</v>
@@ -7721,49 +7721,49 @@
         <v>258.546520175299</v>
       </c>
       <c r="K45" t="n">
-        <v>447.7393362696823</v>
+        <v>483.1925438168522</v>
       </c>
       <c r="L45" t="n">
-        <v>791.3597978648825</v>
+        <v>754.5430054120523</v>
       </c>
       <c r="M45" t="n">
-        <v>949.7103396077417</v>
+        <v>912.8935471549115</v>
       </c>
       <c r="N45" t="n">
-        <v>1155.26062421531</v>
+        <v>1118.44383176248</v>
       </c>
       <c r="O45" t="n">
         <v>1429.756283446199</v>
       </c>
       <c r="P45" t="n">
-        <v>1614.555627915705</v>
+        <v>1614.555627915706</v>
       </c>
       <c r="Q45" t="n">
-        <v>1614.555627915705</v>
+        <v>1614.555627915706</v>
       </c>
       <c r="R45" t="n">
-        <v>1614.555627915705</v>
+        <v>1614.555627915706</v>
       </c>
       <c r="S45" t="n">
-        <v>1614.555627915705</v>
+        <v>1614.555627915706</v>
       </c>
       <c r="T45" t="n">
-        <v>1488.26435852611</v>
+        <v>1614.555627915706</v>
       </c>
       <c r="U45" t="n">
-        <v>1488.26435852611</v>
+        <v>1284.040113006426</v>
       </c>
       <c r="V45" t="n">
-        <v>1143.304088635686</v>
+        <v>939.0798431160017</v>
       </c>
       <c r="W45" t="n">
-        <v>1143.304088635686</v>
+        <v>939.0798431160017</v>
       </c>
       <c r="X45" t="n">
-        <v>1143.304088635686</v>
+        <v>588.7134396358122</v>
       </c>
       <c r="Y45" t="n">
-        <v>813.6158131143379</v>
+        <v>259.0251641144643</v>
       </c>
     </row>
     <row r="46">
@@ -7791,7 +7791,7 @@
         <v>99.67374065245131</v>
       </c>
       <c r="H46" t="n">
-        <v>62.32</v>
+        <v>99.67374065245131</v>
       </c>
       <c r="I46" t="n">
         <v>62.32</v>
@@ -7964,22 +7964,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>51.26150624509023</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>15.5818850760238</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>748.519929016234</v>
       </c>
       <c r="N2" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
-        <v>121.9580983050367</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P2" t="n">
         <v>815.2870600406815</v>
@@ -8204,22 +8204,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>783.0093003026295</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>1096.663422488788</v>
+        <v>883.0371884315869</v>
       </c>
       <c r="O5" t="n">
-        <v>605.4874527373632</v>
+        <v>885.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2870600406814674</v>
+        <v>0.2870600406826043</v>
       </c>
       <c r="Q5" t="n">
         <v>615.8520732695737</v>
@@ -8441,7 +8441,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>503.2488834659011</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
-        <v>1096.663422488788</v>
+        <v>883.0371884315887</v>
       </c>
       <c r="O8" t="n">
         <v>70.24786957409242</v>
@@ -8681,7 +8681,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M11" t="n">
         <v>544.2621276423173</v>
@@ -8690,13 +8690,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>750.7672643616811</v>
+        <v>307.7378754195927</v>
       </c>
       <c r="P11" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,19 +8918,19 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>340.8955523564375</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
-        <v>815.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9152,13 +9152,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>438.3562054605846</v>
       </c>
       <c r="L17" t="n">
-        <v>237.4900058455003</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
         <v>1096.663422488788</v>
@@ -9386,10 +9386,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>151.7858245236418</v>
       </c>
       <c r="K20" t="n">
-        <v>438.3562054605845</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
         <v>815</v>
@@ -9626,10 +9626,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>66.38559440267295</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>815</v>
+        <v>438.3562054605846</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9644,7 +9644,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9866,22 +9866,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>453.2267526751608</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N26" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>849.2478695741167</v>
+        <v>436.8686156341329</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600407058</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,10 +10100,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,13 +10112,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>403.0299382815832</v>
+        <v>129.1842097006017</v>
       </c>
       <c r="P29" t="n">
-        <v>779.2870600407117</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,22 +10337,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>689.2054510344051</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>849.247869574134</v>
+        <v>403.0299382815729</v>
       </c>
       <c r="P32" t="n">
-        <v>779.2870600407231</v>
+        <v>779.2870600407222</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>94.05030929427252</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>731.1613784763049</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,10 +10586,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>849.2478695741536</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>333.069128748142</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10814,16 +10814,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>235.3214156032986</v>
+        <v>394.9069511844208</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>849.2478695741672</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>750.3590157188876</v>
       </c>
       <c r="M41" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>849.2478695742036</v>
+        <v>849.2478695742032</v>
       </c>
       <c r="P41" t="n">
-        <v>779.2870600407927</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>363.0583549104633</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11285,22 +11285,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>688.2341332417827</v>
+        <v>779</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>675.2066789423629</v>
       </c>
       <c r="N44" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>849.24786957425</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>779.287060040839</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -23223,10 +23223,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.9993129555745</v>
+        <v>195.3068282048581</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -23235,13 +23235,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23271,10 +23271,10 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23283,7 +23283,7 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>42.69266915316098</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -23387,16 +23387,16 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>107.2354541721786</v>
       </c>
       <c r="M13" t="n">
         <v>295.6316114025499</v>
@@ -23420,7 +23420,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>138.1895383916304</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
         <v>462.4478973282775</v>
@@ -23627,7 +23627,7 @@
         <v>6.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -23654,19 +23654,19 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O16" t="n">
         <v>361.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>69.04626797189968</v>
       </c>
       <c r="Q16" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>363.9751096360941</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>83.37347970285543</v>
@@ -23891,22 +23891,22 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O19" t="n">
         <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>69.04626797189968</v>
       </c>
       <c r="R19" t="n">
         <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>36.15692561816253</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24092,7 +24092,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -24131,16 +24131,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>361.445564079015</v>
+        <v>22.80679627819029</v>
       </c>
       <c r="P22" t="n">
-        <v>77.16006830897823</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24365,19 +24365,19 @@
         <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>361.2313432435845</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,19 +24408,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>101.2743021721436</v>
+        <v>182.0819782497391</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -24462,7 +24462,7 @@
         <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24584,7 +24584,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24611,10 +24611,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>154.918530996742</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
@@ -24663,7 +24663,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>10.25860861458553</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24699,7 +24699,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>10.25860861458551</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -24842,19 +24842,19 @@
         <v>283.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>352.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>296.5380537915477</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>437.839266425598</v>
+        <v>56.85733851270868</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>74.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>10.25860861458553</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>10.25860861458523</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25079,19 +25079,19 @@
         <v>283.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>296.5380537915476</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>370.14867193885</v>
+        <v>437.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>74.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25122,7 +25122,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>10.25860861458554</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -25182,7 +25182,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>10.25860861458574</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -25359,7 +25359,7 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>10.25860861458554</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -25425,7 +25425,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>10.25860861458563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -25547,7 +25547,7 @@
         <v>135.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>232.6316114025499</v>
       </c>
       <c r="N40" t="n">
         <v>283.1850752716849</v>
@@ -25556,16 +25556,16 @@
         <v>352.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>175.9612395595296</v>
+        <v>399.4478973282775</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>438.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>74.37347970285543</v>
+        <v>56.85733851270872</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25593,10 +25593,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>138.8668531847576</v>
       </c>
       <c r="C41" t="n">
-        <v>259.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -25605,13 +25605,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>68.24776577267639</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>218.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,7 +25641,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>60.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -25650,13 +25650,13 @@
         <v>396.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>459.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>439.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>448.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>194.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -25684,13 +25684,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>149.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>135.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>19.42448031653375</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,22 +25720,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>137.9877901520043</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>276.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>215.3577652175138</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>210.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>242.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25796,7 +25796,7 @@
         <v>497.4478973282775</v>
       </c>
       <c r="Q43" t="n">
-        <v>332.8221323210453</v>
+        <v>535.839266425598</v>
       </c>
       <c r="R43" t="n">
         <v>536.6021279811511</v>
@@ -25805,13 +25805,13 @@
         <v>172.3734797028554</v>
       </c>
       <c r="T43" t="n">
-        <v>20.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>9.170310216216194</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
         <v>36.37280983870968</v>
@@ -25833,10 +25833,10 @@
         <v>408.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>376.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>337.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -25845,13 +25845,13 @@
         <v>331.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>330.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>335.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>77.08115968268461</v>
+        <v>72.78951209217976</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25881,16 +25881,16 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>421.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>17.75518201516064</v>
+        <v>513.6755817285639</v>
       </c>
       <c r="U44" t="n">
         <v>576.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>556.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -25909,10 +25909,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>260.9448300643555</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>288.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>274.9376868977026</v>
@@ -25963,10 +25963,10 @@
         <v>393.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>207.3294085218145</v>
+        <v>332.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>327.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -25975,7 +25975,7 @@
         <v>359.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>346.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -26006,10 +26006,10 @@
         <v>172.04387284153</v>
       </c>
       <c r="H46" t="n">
-        <v>118.7909228556918</v>
+        <v>155.7711261016186</v>
       </c>
       <c r="I46" t="n">
-        <v>103.6334556201183</v>
+        <v>66.65325237419147</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2091884.882817422</v>
+        <v>2091884.882817421</v>
       </c>
     </row>
     <row r="4">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3939393.487653977</v>
+        <v>3939393.487653976</v>
       </c>
     </row>
     <row r="6">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5829138.404644066</v>
+        <v>5829138.404644064</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6774010.863139105</v>
+        <v>6774010.863139103</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7718883.321634145</v>
+        <v>7718883.321634143</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8580056.265062468</v>
+        <v>8580056.265062466</v>
       </c>
     </row>
     <row r="11">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12372943.62786991</v>
+        <v>12372943.6278699</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13161652.0070501</v>
+        <v>13161652.00705009</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13696744.33530786</v>
+        <v>13696744.33530785</v>
       </c>
     </row>
   </sheetData>
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324281</v>
       </c>
       <c r="C2" t="n">
         <v>1227892.61432428</v>
       </c>
       <c r="D2" t="n">
-        <v>1227892.614324281</v>
+        <v>1227892.61432428</v>
       </c>
       <c r="E2" t="n">
         <v>1098179.486216543</v>
@@ -26299,7 +26299,7 @@
         <v>1192917.563917558</v>
       </c>
       <c r="L2" t="n">
-        <v>1192917.563917558</v>
+        <v>1192917.563917559</v>
       </c>
       <c r="M2" t="n">
         <v>1192917.563917558</v>
@@ -26308,10 +26308,10 @@
         <v>1192917.563917558</v>
       </c>
       <c r="O2" t="n">
-        <v>992272.7745722493</v>
+        <v>992272.7745722489</v>
       </c>
       <c r="P2" t="n">
-        <v>673180.6710339502</v>
+        <v>673180.6710339505</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>575920.3474495772</v>
+        <v>580809.5038374891</v>
       </c>
       <c r="C4" t="n">
-        <v>574167.5049491362</v>
+        <v>579056.661337048</v>
       </c>
       <c r="D4" t="n">
-        <v>572412.2846084388</v>
+        <v>577301.4409963507</v>
       </c>
       <c r="E4" t="n">
-        <v>493973.8046613695</v>
+        <v>498813.3005071199</v>
       </c>
       <c r="F4" t="n">
-        <v>544553.626856441</v>
+        <v>549393.1227021916</v>
       </c>
       <c r="G4" t="n">
-        <v>542883.6451658959</v>
+        <v>547723.1410116464</v>
       </c>
       <c r="H4" t="n">
-        <v>541211.3456360602</v>
+        <v>546050.8414818107</v>
       </c>
       <c r="I4" t="n">
-        <v>539536.711548938</v>
+        <v>544376.2073946884</v>
       </c>
       <c r="J4" t="n">
-        <v>483585.363292172</v>
+        <v>488315.773108913</v>
       </c>
       <c r="K4" t="n">
-        <v>541594.413008231</v>
+        <v>546325.566147172</v>
       </c>
       <c r="L4" t="n">
-        <v>539876.9064614967</v>
+        <v>544608.0596004378</v>
       </c>
       <c r="M4" t="n">
-        <v>538156.94513248</v>
+        <v>542888.098271421</v>
       </c>
       <c r="N4" t="n">
-        <v>536434.5107850763</v>
+        <v>541165.6639240172</v>
       </c>
       <c r="O4" t="n">
-        <v>423119.5490721907</v>
+        <v>427849.9588889317</v>
       </c>
       <c r="P4" t="n">
-        <v>244559.8802791928</v>
+        <v>249290.2900959339</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>281912.6668747031</v>
+        <v>277023.5104867915</v>
       </c>
       <c r="C6" t="n">
-        <v>570545.5093751437</v>
+        <v>565656.3529872316</v>
       </c>
       <c r="D6" t="n">
-        <v>572300.7297158417</v>
+        <v>567411.5733279294</v>
       </c>
       <c r="E6" t="n">
-        <v>355738.1565551733</v>
+        <v>350898.6607094234</v>
       </c>
       <c r="F6" t="n">
-        <v>527949.6344437751</v>
+        <v>523110.1385980246</v>
       </c>
       <c r="G6" t="n">
-        <v>572819.6161343204</v>
+        <v>567980.1202885697</v>
       </c>
       <c r="H6" t="n">
-        <v>574491.9156641561</v>
+        <v>569652.4198184056</v>
       </c>
       <c r="I6" t="n">
-        <v>576166.5497512779</v>
+        <v>571327.0539055277</v>
       </c>
       <c r="J6" t="n">
-        <v>126464.597956371</v>
+        <v>121734.1881396298</v>
       </c>
       <c r="K6" t="n">
-        <v>486148.0789093275</v>
+        <v>481416.9257703864</v>
       </c>
       <c r="L6" t="n">
-        <v>581465.5854560616</v>
+        <v>576734.4323171208</v>
       </c>
       <c r="M6" t="n">
-        <v>583185.5467850784</v>
+        <v>578454.3936461373</v>
       </c>
       <c r="N6" t="n">
-        <v>584907.9811324816</v>
+        <v>580176.8279935411</v>
       </c>
       <c r="O6" t="n">
-        <v>447416.9155000586</v>
+        <v>442686.5056833173</v>
       </c>
       <c r="P6" t="n">
-        <v>375120.5537547574</v>
+        <v>370390.1439380166</v>
       </c>
     </row>
   </sheetData>
@@ -26990,7 +26990,7 @@
         <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27439,13 +27439,13 @@
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>303.5095671255647</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>52.63096829726969</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,13 +27481,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>365.2859755662879</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27575,7 +27575,7 @@
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>400</v>
+        <v>143.9573181542525</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27591,34 +27591,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
-        <v>376.2873881041736</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
         <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>330.4312420859801</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27648,19 +27648,19 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27673,13 +27673,13 @@
         <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="D5" t="n">
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>52.63096829727004</v>
+        <v>303.5095671255648</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27718,13 +27718,13 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27736,10 +27736,10 @@
         <v>400</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6">
@@ -27749,22 +27749,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>155.5878407271842</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27818,7 +27818,7 @@
         <v>400</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="7">
@@ -27831,13 +27831,13 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
@@ -27846,10 +27846,10 @@
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
@@ -27885,7 +27885,7 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>243.4244847994877</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>400</v>
@@ -27894,7 +27894,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>344.1645237617653</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>303.5095671255648</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27955,16 +27955,16 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>52.63096829726999</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V8" t="n">
         <v>400</v>
@@ -27989,7 +27989,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
@@ -28043,16 +28043,16 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>303.3742880620966</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>342.2743756165773</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,34 +28065,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
+        <v>35.26894883590776</v>
+      </c>
+      <c r="K10" t="n">
         <v>400</v>
-      </c>
-      <c r="K10" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28122,19 +28122,19 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
-        <v>372.4787686000883</v>
+        <v>237.3445329349385</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28250,7 +28250,7 @@
         <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>19.1168712588393</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28262,13 +28262,13 @@
         <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>71.03760616835959</v>
+        <v>225</v>
       </c>
       <c r="P12" t="n">
         <v>225</v>
       </c>
       <c r="Q12" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R12" t="n">
         <v>225</v>
@@ -28390,7 +28390,7 @@
         <v>279</v>
       </c>
       <c r="E14" t="n">
-        <v>275.549808614586</v>
+        <v>279</v>
       </c>
       <c r="F14" t="n">
         <v>279</v>
@@ -28399,7 +28399,7 @@
         <v>279</v>
       </c>
       <c r="H14" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="I14" t="n">
         <v>150.0811596826846</v>
@@ -28484,28 +28484,28 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>217.5442043757545</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>279</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>279</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>217.5442043757548</v>
       </c>
       <c r="R15" t="n">
         <v>279</v>
@@ -28639,7 +28639,7 @@
         <v>279</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6309682972706</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>247.42840744288</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
         <v>279</v>
@@ -28718,11 +28718,11 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
+        <v>261.5913251766234</v>
+      </c>
+      <c r="J18" t="n">
         <v>279</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
@@ -28730,19 +28730,19 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>279</v>
       </c>
-      <c r="N18" t="n">
-        <v>155.670590267103</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28873,7 +28873,7 @@
         <v>279</v>
       </c>
       <c r="H20" t="n">
-        <v>275.549808614586</v>
+        <v>279</v>
       </c>
       <c r="I20" t="n">
         <v>150.0811596826846</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988282945</v>
+        <v>247.42840744288</v>
       </c>
       <c r="S20" t="n">
         <v>279</v>
@@ -28955,7 +28955,7 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -28964,19 +28964,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>155.6705902671029</v>
       </c>
       <c r="N21" t="n">
-        <v>217.5442043757545</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29110,7 +29110,7 @@
         <v>279</v>
       </c>
       <c r="H23" t="n">
-        <v>279</v>
+        <v>275.549808614586</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29143,7 +29143,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
-        <v>275.5498086145856</v>
+        <v>279</v>
       </c>
       <c r="T23" t="n">
         <v>279</v>
@@ -29192,13 +29192,13 @@
         <v>279</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>279</v>
       </c>
       <c r="J24" t="n">
         <v>279</v>
       </c>
       <c r="K24" t="n">
-        <v>217.5442043757545</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -29207,7 +29207,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>155.6705902671032</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -29435,10 +29435,10 @@
         <v>225</v>
       </c>
       <c r="K27" t="n">
-        <v>19.11687125883918</v>
+        <v>225</v>
       </c>
       <c r="L27" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="M27" t="n">
         <v>225</v>
@@ -29675,7 +29675,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>176.7238924533193</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -29684,7 +29684,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>176.7238924533191</v>
       </c>
       <c r="P30" t="n">
         <v>288</v>
@@ -29906,19 +29906,19 @@
         <v>288</v>
       </c>
       <c r="J33" t="n">
-        <v>105.8502783446678</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>105.8502783446675</v>
       </c>
       <c r="N33" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -30140,7 +30140,7 @@
         <v>288</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>278.9295434351469</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30149,22 +30149,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>288</v>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>176.7238924533191</v>
-      </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>288</v>
       </c>
       <c r="R36" t="n">
         <v>288</v>
@@ -30377,13 +30377,13 @@
         <v>288</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>288</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>176.723892453319</v>
+        <v>288</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -30395,13 +30395,13 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>173.0792650904796</v>
+        <v>278.929543435147</v>
       </c>
       <c r="R39" t="n">
         <v>288</v>
@@ -30617,10 +30617,10 @@
         <v>190</v>
       </c>
       <c r="J42" t="n">
+        <v>78.53719264813093</v>
+      </c>
+      <c r="K42" t="n">
         <v>190</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>190</v>
@@ -30632,13 +30632,13 @@
         <v>190</v>
       </c>
       <c r="O42" t="n">
-        <v>185.0702558825936</v>
+        <v>190</v>
       </c>
       <c r="P42" t="n">
         <v>190</v>
       </c>
       <c r="Q42" t="n">
-        <v>173.0792650904796</v>
+        <v>190</v>
       </c>
       <c r="R42" t="n">
         <v>190</v>
@@ -30693,10 +30693,10 @@
         <v>190</v>
       </c>
       <c r="I43" t="n">
-        <v>190</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>190</v>
+        <v>65.05659981282227</v>
       </c>
       <c r="K43" t="n">
         <v>190</v>
@@ -30729,7 +30729,7 @@
         <v>190</v>
       </c>
       <c r="U43" t="n">
-        <v>190</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
         <v>190</v>
@@ -30857,10 +30857,10 @@
         <v>73</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>35.81132075471698</v>
       </c>
       <c r="L45" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>73</v>
@@ -30869,7 +30869,7 @@
         <v>73</v>
       </c>
       <c r="O45" t="n">
-        <v>35.81132075471698</v>
+        <v>73</v>
       </c>
       <c r="P45" t="n">
         <v>73</v>
@@ -34746,7 +34746,7 @@
         <v>815</v>
       </c>
       <c r="K2" t="n">
-        <v>783.0093003026975</v>
+        <v>783.0093003026868</v>
       </c>
       <c r="L2" t="n">
         <v>815</v>
@@ -34877,34 +34877,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>147.516262002555</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
         <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>41.91046828483709</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34934,19 +34934,19 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,10 +34983,10 @@
         <v>815</v>
       </c>
       <c r="K5" t="n">
+        <v>783.0093003025816</v>
+      </c>
+      <c r="L5" t="n">
         <v>815</v>
-      </c>
-      <c r="L5" t="n">
-        <v>783.0093003026295</v>
       </c>
       <c r="M5" t="n">
         <v>815</v>
@@ -34998,7 +34998,7 @@
         <v>815</v>
       </c>
       <c r="P5" t="n">
-        <v>815</v>
+        <v>815.0000000000011</v>
       </c>
       <c r="Q5" t="n">
         <v>815</v>
@@ -35117,13 +35117,13 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -35132,10 +35132,10 @@
         <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -35171,7 +35171,7 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>92.46609352502981</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>200.8296897837838</v>
@@ -35180,7 +35180,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>96.72087833165776</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35223,7 +35223,7 @@
         <v>815</v>
       </c>
       <c r="L8" t="n">
-        <v>783.0093003026898</v>
+        <v>783.0093003026169</v>
       </c>
       <c r="M8" t="n">
         <v>815</v>
@@ -35238,7 +35238,7 @@
         <v>815</v>
       </c>
       <c r="Q8" t="n">
-        <v>815.0000000000011</v>
+        <v>815</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,34 +35351,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35408,19 +35408,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>173.3084583838721</v>
+        <v>38.17422271872228</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35460,7 +35460,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -35469,13 +35469,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>680.5193947875886</v>
+        <v>237.4900058455002</v>
       </c>
       <c r="P11" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35536,7 +35536,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>416.1038546407913</v>
+        <v>210.2207258996306</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35548,13 +35548,13 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>312.494628071106</v>
+        <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
         <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35697,19 +35697,19 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L14" t="n">
-        <v>340.8955523564375</v>
+        <v>536.481087937485</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>815</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35770,28 +35770,28 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>342.7528106134302</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>470.1038546407913</v>
       </c>
       <c r="L15" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N15" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>44.46493928527515</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35931,13 +35931,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230996</v>
+        <v>438.3562054605846</v>
       </c>
       <c r="L17" t="n">
-        <v>237.4900058455003</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
         <v>619.4144644189528</v>
@@ -36004,10 +36004,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>61.87361410865147</v>
+        <v>44.4649392852749</v>
       </c>
       <c r="J18" t="n">
-        <v>125.2086062376757</v>
+        <v>404.2086062376757</v>
       </c>
       <c r="K18" t="n">
         <v>191.1038546407913</v>
@@ -36016,19 +36016,19 @@
         <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>290.2971403757578</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P18" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,10 +36165,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>116.7428182785515</v>
       </c>
       <c r="K20" t="n">
-        <v>438.3562054605845</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
         <v>815</v>
@@ -36241,7 +36241,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J21" t="n">
         <v>125.2086062376757</v>
@@ -36250,19 +36250,19 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>274.091375348687</v>
+        <v>553.0913753486871</v>
       </c>
       <c r="M21" t="n">
-        <v>86.95004216450428</v>
+        <v>242.6206324316071</v>
       </c>
       <c r="N21" t="n">
-        <v>352.1707544844093</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>392.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36405,10 +36405,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>66.38559440267295</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>815</v>
+        <v>438.3562054605846</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36423,7 +36423,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36478,13 +36478,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>61.87361410865147</v>
       </c>
       <c r="J24" t="n">
         <v>404.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>408.6480590165459</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
@@ -36493,7 +36493,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>134.6265501086548</v>
+        <v>290.297140375758</v>
       </c>
       <c r="O24" t="n">
         <v>241.4570219027464</v>
@@ -36645,22 +36645,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>453.2267526751608</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
+        <v>366.6207460600403</v>
+      </c>
+      <c r="P26" t="n">
         <v>779.0000000000243</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36721,10 +36721,10 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M27" t="n">
         <v>311.9500421645043</v>
@@ -36879,10 +36879,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>47.83862152375355</v>
+        <v>764.7137390467999</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,13 +36891,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>332.7820687074907</v>
+        <v>58.93634012650926</v>
       </c>
       <c r="P29" t="n">
-        <v>779.0000000000302</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36961,7 +36961,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>450.8152678020062</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M30" t="n">
         <v>86.95004216450428</v>
@@ -36970,7 +36970,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O30" t="n">
-        <v>241.4570219027464</v>
+        <v>418.1809143560654</v>
       </c>
       <c r="P30" t="n">
         <v>401.6660045146532</v>
@@ -37116,22 +37116,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>689.2054510344051</v>
+        <v>47.83862152375355</v>
       </c>
       <c r="L32" t="n">
-        <v>47.83862152371148</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>779.0000000000416</v>
+        <v>332.7820687074804</v>
       </c>
       <c r="P32" t="n">
-        <v>779.0000000000416</v>
+        <v>779.0000000000407</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37192,19 +37192,19 @@
         <v>70.87361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>231.0588845823436</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>191.1038546407913</v>
+        <v>479.1038546407913</v>
       </c>
       <c r="L33" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M33" t="n">
-        <v>86.95004216450428</v>
+        <v>192.8003205091718</v>
       </c>
       <c r="N33" t="n">
-        <v>422.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O33" t="n">
         <v>241.4570219027464</v>
@@ -37350,13 +37350,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>395.2617303410664</v>
+        <v>59.00730304918219</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>47.83862152377594</v>
+        <v>779</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
@@ -37365,10 +37365,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O35" t="n">
-        <v>779.0000000000612</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>332.7820687074607</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>443.0293889420883</v>
@@ -37426,7 +37426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>61.80315754379838</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
@@ -37435,7 +37435,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>562.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
         <v>86.95004216450428</v>
@@ -37447,10 +37447,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>290.3898969679723</v>
+        <v>401.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>114.9207349095204</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37593,16 +37593,16 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L38" t="n">
-        <v>283.1600371270074</v>
+        <v>442.7455727081297</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O38" t="n">
-        <v>779.0000000000748</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37663,13 +37663,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>70.87361410865147</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
-        <v>367.8277470941104</v>
+        <v>479.1038546407913</v>
       </c>
       <c r="L39" t="n">
         <v>274.091375348687</v>
@@ -37681,13 +37681,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O39" t="n">
-        <v>529.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>105.8502783446673</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>750.3590157188876</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>779.0000000001112</v>
+        <v>779.0000000001107</v>
       </c>
       <c r="P41" t="n">
-        <v>779.0000000001112</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>190.2356705829779</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37903,10 +37903,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>315.2086062376757</v>
+        <v>203.7457988858066</v>
       </c>
       <c r="K42" t="n">
-        <v>191.1038546407913</v>
+        <v>381.1038546407913</v>
       </c>
       <c r="L42" t="n">
         <v>464.091375348687</v>
@@ -37918,13 +37918,13 @@
         <v>324.6265501086548</v>
       </c>
       <c r="O42" t="n">
-        <v>426.52727778534</v>
+        <v>431.4570219027464</v>
       </c>
       <c r="P42" t="n">
         <v>303.6660045146532</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>16.92073490952041</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>13.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>154.7310511640922</v>
+        <v>29.78765097691451</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>39.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38064,22 +38064,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L44" t="n">
-        <v>688.2341332417827</v>
+        <v>779</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>130.9445513000456</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>779.0000000001576</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>779.0000000001576</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38143,10 +38143,10 @@
         <v>198.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>191.1038546407913</v>
+        <v>226.9151753955083</v>
       </c>
       <c r="L45" t="n">
-        <v>347.091375348687</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M45" t="n">
         <v>159.9500421645043</v>
@@ -38155,7 +38155,7 @@
         <v>207.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>277.2683426574633</v>
+        <v>314.4570219027464</v>
       </c>
       <c r="P45" t="n">
         <v>186.6660045146532</v>
